--- a/data/trans_dic/P23_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,63; 47,23</t>
+          <t>39,51; 47,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,24; 40,58</t>
+          <t>33,15; 40,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,51</t>
+          <t>33,58; 40,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 32,21</t>
+          <t>24,35; 32,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,88; 26,41</t>
+          <t>19,97; 26,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,81; 26,44</t>
+          <t>19,98; 26,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,85; 28,47</t>
+          <t>21,85; 28,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 20,89</t>
+          <t>15,8; 20,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,88; 35,78</t>
+          <t>30,86; 35,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,68; 32,86</t>
+          <t>27,55; 32,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,5; 33,89</t>
+          <t>28,33; 33,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,69; 25,26</t>
+          <t>20,87; 25,27</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 43,39</t>
+          <t>36,8; 43,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,96; 40,49</t>
+          <t>34,18; 40,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,07; 35,84</t>
+          <t>29,82; 35,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 26,07</t>
+          <t>8,7; 26,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,04; 25,6</t>
+          <t>20,21; 25,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,2; 30,95</t>
+          <t>25,05; 30,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,33; 29,05</t>
+          <t>23,44; 28,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,55; 21,23</t>
+          <t>16,68; 21,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 33,93</t>
+          <t>29,52; 33,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 34,78</t>
+          <t>30,42; 34,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,24; 31,37</t>
+          <t>27,26; 31,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 22,63</t>
+          <t>12,97; 22,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,61; 39,95</t>
+          <t>32,58; 40,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,33; 41,04</t>
+          <t>33,51; 40,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,23; 44,67</t>
+          <t>36,7; 44,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,65; 33,31</t>
+          <t>24,67; 33,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,62; 27,1</t>
+          <t>20,77; 27,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,55; 32,46</t>
+          <t>25,23; 31,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,25; 32,14</t>
+          <t>25,74; 32,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 22,47</t>
+          <t>8,25; 22,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,46; 32,67</t>
+          <t>27,63; 32,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,17; 35,3</t>
+          <t>30,16; 35,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,15; 36,98</t>
+          <t>32,25; 37,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 25,67</t>
+          <t>13,81; 25,9</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,74; 43,11</t>
+          <t>36,68; 42,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,79; 39,09</t>
+          <t>32,87; 39,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,95; 32,98</t>
+          <t>27,47; 33,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 26,72</t>
+          <t>20,69; 26,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 30,45</t>
+          <t>24,83; 30,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,76; 30,38</t>
+          <t>24,55; 30,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 27,64</t>
+          <t>22,03; 27,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,17; 20,15</t>
+          <t>14,06; 20,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,04; 35,3</t>
+          <t>31,19; 35,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,35; 33,53</t>
+          <t>29,33; 33,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,2; 29,18</t>
+          <t>25,28; 29,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 22,36</t>
+          <t>17,8; 22,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,0; 41,57</t>
+          <t>38,25; 41,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,21; 38,77</t>
+          <t>35,12; 38,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,99; 36,39</t>
+          <t>32,98; 36,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,25; 26,8</t>
+          <t>19,06; 26,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,23; 26,21</t>
+          <t>23,11; 25,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,37; 28,5</t>
+          <t>25,46; 28,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,6; 27,56</t>
+          <t>24,57; 27,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 19,5</t>
+          <t>14,79; 19,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,89; 33,31</t>
+          <t>30,93; 33,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,6; 32,99</t>
+          <t>30,69; 32,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,37</t>
+          <t>29,08; 31,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 22,57</t>
+          <t>17,91; 22,56</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>275047; 327757</t>
+          <t>274201; 331213</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>233863; 285479</t>
+          <t>233231; 286717</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>225737; 273338</t>
+          <t>226604; 274142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156092; 204343</t>
+          <t>154487; 204897</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>136854; 181816</t>
+          <t>137479; 181664</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>138054; 184324</t>
+          <t>139298; 185614</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>146785; 191230</t>
+          <t>146763; 192002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>105781; 141166</t>
+          <t>106760; 140033</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>426836; 494661</t>
+          <t>426574; 494209</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>387643; 460146</t>
+          <t>385859; 456953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>383813; 456358</t>
+          <t>381533; 453962</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>271121; 330912</t>
+          <t>273434; 331091</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>355472; 416893</t>
+          <t>353568; 417826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>345319; 411719</t>
+          <t>347623; 411421</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>307130; 366063</t>
+          <t>304565; 366431</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125353; 310683</t>
+          <t>103671; 311969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194065; 247876</t>
+          <t>195716; 249589</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>260104; 319449</t>
+          <t>258600; 318886</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>243123; 302717</t>
+          <t>244246; 300278</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>158536; 203394</t>
+          <t>159841; 205444</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>570411; 654488</t>
+          <t>569447; 652858</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>623222; 712663</t>
+          <t>623267; 712581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>562031; 647181</t>
+          <t>562462; 645876</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>294979; 486500</t>
+          <t>278951; 484235</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>221242; 271059</t>
+          <t>221083; 272965</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>252541; 310962</t>
+          <t>253889; 307706</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282430; 338898</t>
+          <t>278434; 334659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173654; 234679</t>
+          <t>173780; 235038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>141004; 185290</t>
+          <t>142014; 186162</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>198306; 251946</t>
+          <t>195859; 248020</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>197697; 251590</t>
+          <t>201555; 252319</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85631; 209688</t>
+          <t>77029; 209221</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>374130; 445127</t>
+          <t>376414; 443487</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>462691; 541492</t>
+          <t>462627; 538756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>495680; 570007</t>
+          <t>497149; 576479</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>235844; 420404</t>
+          <t>226181; 424162</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>346130; 406158</t>
+          <t>345619; 403481</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310744; 370497</t>
+          <t>311519; 373556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>252683; 309222</t>
+          <t>257545; 314330</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190046; 247643</t>
+          <t>191752; 246233</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>256471; 316218</t>
+          <t>257874; 316263</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>260235; 319279</t>
+          <t>258001; 317420</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>230990; 288153</t>
+          <t>229682; 286428</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>154643; 219796</t>
+          <t>153356; 219540</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>614911; 699192</t>
+          <t>617821; 702468</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>586676; 670061</t>
+          <t>586123; 672261</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>498984; 577710</t>
+          <t>500583; 580701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>360864; 451287</t>
+          <t>359160; 448809</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1244842; 1361477</t>
+          <t>1252736; 1365380</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1206177; 1328041</t>
+          <t>1203028; 1319774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1119083; 1234664</t>
+          <t>1118666; 1233119</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>665502; 926490</t>
+          <t>659122; 919495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>785050; 885840</t>
+          <t>781070; 876985</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>902400; 1013655</t>
+          <t>905512; 1012153</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>870508; 975209</t>
+          <t>869521; 974405</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>525297; 713537</t>
+          <t>541235; 718797</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2055957; 2216426</t>
+          <t>2058038; 2217789</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2136501; 2303716</t>
+          <t>2142650; 2302854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2015020; 2174439</t>
+          <t>2015671; 2174376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1287875; 1605712</t>
+          <t>1274431; 1605487</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,51; 47,72</t>
+          <t>39,69; 47,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,15; 40,76</t>
+          <t>33,4; 41,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,63</t>
+          <t>33,34; 40,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,35; 32,3</t>
+          <t>24,35; 31,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 26,39</t>
+          <t>20,26; 26,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 26,63</t>
+          <t>19,76; 26,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,85; 28,58</t>
+          <t>21,76; 28,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 20,72</t>
+          <t>15,4; 20,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,86; 35,75</t>
+          <t>30,76; 35,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,55; 32,63</t>
+          <t>27,51; 32,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 33,71</t>
+          <t>28,4; 33,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,87; 25,27</t>
+          <t>20,61; 25,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,8; 43,49</t>
+          <t>36,69; 42,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 40,46</t>
+          <t>34,39; 40,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 35,88</t>
+          <t>29,87; 35,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 26,17</t>
+          <t>21,31; 27,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,21; 25,77</t>
+          <t>20,04; 25,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,05; 30,89</t>
+          <t>25,12; 31,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,44; 28,82</t>
+          <t>23,22; 28,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 21,44</t>
+          <t>16,18; 20,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,52; 33,84</t>
+          <t>29,39; 33,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,42; 34,78</t>
+          <t>30,58; 34,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,26; 31,3</t>
+          <t>27,36; 31,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 22,52</t>
+          <t>19,44; 23,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,58; 40,23</t>
+          <t>32,35; 40,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 40,61</t>
+          <t>33,54; 40,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,7; 44,11</t>
+          <t>37,21; 44,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,67; 33,36</t>
+          <t>23,34; 30,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,77; 27,22</t>
+          <t>20,91; 27,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,23; 31,95</t>
+          <t>25,07; 32,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 32,23</t>
+          <t>25,48; 31,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 22,42</t>
+          <t>18,87; 24,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,63; 32,55</t>
+          <t>27,43; 32,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,16; 35,13</t>
+          <t>30,34; 35,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,25; 37,4</t>
+          <t>32,18; 37,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 25,9</t>
+          <t>21,81; 26,62</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,68; 42,82</t>
+          <t>36,25; 42,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,87; 39,42</t>
+          <t>32,79; 39,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,47; 33,53</t>
+          <t>27,12; 33,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 26,57</t>
+          <t>21,3; 27,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,83; 30,45</t>
+          <t>24,56; 30,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,55; 30,2</t>
+          <t>24,52; 30,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,03; 27,48</t>
+          <t>22,09; 27,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 20,12</t>
+          <t>16,78; 20,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,19; 35,46</t>
+          <t>31,14; 35,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,33; 33,64</t>
+          <t>29,25; 33,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 29,33</t>
+          <t>25,2; 29,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 22,24</t>
+          <t>19,56; 23,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,25; 41,68</t>
+          <t>38,16; 41,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,12; 38,53</t>
+          <t>35,25; 38,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,98; 36,35</t>
+          <t>33,22; 36,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 26,59</t>
+          <t>24,02; 27,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,11; 25,95</t>
+          <t>23,14; 26,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,46; 28,46</t>
+          <t>25,35; 28,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,57; 27,53</t>
+          <t>24,58; 27,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,65</t>
+          <t>17,85; 20,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,93; 33,33</t>
+          <t>30,98; 33,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,69; 32,98</t>
+          <t>30,66; 33,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,37</t>
+          <t>29,14; 31,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,91; 22,56</t>
+          <t>21,06; 23,18</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178017</t>
+          <t>192912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>322804</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>274201; 331213</t>
+          <t>275419; 326549</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>233231; 286717</t>
+          <t>234972; 288879</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226604; 274142</t>
+          <t>224999; 275259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154487; 204897</t>
+          <t>167906; 219871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>137479; 181664</t>
+          <t>139435; 182015</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>139298; 185614</t>
+          <t>137762; 185351</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>146763; 192002</t>
+          <t>146148; 191320</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>106760; 140033</t>
+          <t>112918; 148620</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>426574; 494209</t>
+          <t>425250; 495737</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385859; 456953</t>
+          <t>385324; 455685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>381533; 453962</t>
+          <t>382396; 453144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>273434; 331091</t>
+          <t>293263; 358349</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238002</t>
+          <t>254952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>180117</t>
+          <t>195819</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>418118</t>
+          <t>450771</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>353568; 417826</t>
+          <t>352541; 412999</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>347623; 411421</t>
+          <t>349765; 413718</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>304565; 366431</t>
+          <t>305033; 364371</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103671; 311969</t>
+          <t>223250; 286341</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>195716; 249589</t>
+          <t>194030; 246244</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>258600; 318886</t>
+          <t>259323; 323274</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>244246; 300278</t>
+          <t>241982; 300105</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>159841; 205444</t>
+          <t>173257; 222370</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>569447; 652858</t>
+          <t>566932; 650349</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>623267; 712581</t>
+          <t>626712; 716316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>562462; 645876</t>
+          <t>564497; 646184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>278951; 484235</t>
+          <t>411834; 489643</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200999</t>
+          <t>214326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>173921</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>357112</t>
+          <t>388248</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>221083; 272965</t>
+          <t>219521; 273651</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>253889; 307706</t>
+          <t>254094; 308245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>278434; 334659</t>
+          <t>282319; 339584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173780; 235038</t>
+          <t>187196; 246765</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>142014; 186162</t>
+          <t>142993; 187523</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>195859; 248020</t>
+          <t>194619; 249467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>201555; 252319</t>
+          <t>199443; 249815</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77029; 209221</t>
+          <t>153266; 198519</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>376414; 443487</t>
+          <t>373756; 443332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>462627; 538756</t>
+          <t>465288; 543670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>497149; 576479</t>
+          <t>496042; 573219</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>226181; 424162</t>
+          <t>351999; 429674</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217493</t>
+          <t>239558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>193193</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>447140</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>345619; 403481</t>
+          <t>341557; 402447</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311519; 373556</t>
+          <t>310726; 370657</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>257545; 314330</t>
+          <t>254293; 311049</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>191752; 246233</t>
+          <t>210915; 270147</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>257874; 316263</t>
+          <t>255066; 312989</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>258001; 317420</t>
+          <t>257671; 316620</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>229682; 286428</t>
+          <t>230295; 284468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>153356; 219540</t>
+          <t>187111; 233878</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>617821; 702468</t>
+          <t>616776; 701247</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>586123; 672261</t>
+          <t>584666; 668509</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>500583; 580701</t>
+          <t>498943; 577694</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>359160; 448809</t>
+          <t>411698; 485931</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>901748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>651946</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1486457</t>
+          <t>1608962</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1252736; 1365380</t>
+          <t>1249910; 1361442</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1203028; 1319774</t>
+          <t>1207570; 1324861</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1118666; 1233119</t>
+          <t>1127117; 1237940</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>659122; 919495</t>
+          <t>847849; 964672</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>781070; 876985</t>
+          <t>782094; 883362</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>905512; 1012153</t>
+          <t>901501; 1014393</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>869521; 974405</t>
+          <t>869748; 982473</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>541235; 718797</t>
+          <t>666059; 753555</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2058038; 2217789</t>
+          <t>2061715; 2208510</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2142650; 2302854</t>
+          <t>2140869; 2304193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2015671; 2174376</t>
+          <t>2019716; 2177719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1274431; 1605487</t>
+          <t>1528923; 1683254</t>
         </is>
       </c>
     </row>
